--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_014/extracted.xlsx
@@ -279,6 +279,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -354,21 +359,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -404,6 +394,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -514,52 +509,17 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G6" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1301,17 +1261,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Guidance Electronics Thermal Upgrade (GETU) — CHT Cold-Plate Model</t>
+          <t>GETU CHT Cold-Plate Cooling Model</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict avionics component temperatures and coolant-side deltas to assess margin vs. 85 C part limit</t>
+          <t>Predict avionics component temperatures and coolant-side deltas to assess margin vs 85 C part limit</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer (CHT) simulation of a 250 W avionics stack cooled by an aluminum cold plate with serpentine channels and a brushless fan. The model predicts peak junction temperatures (notably U3 ASIC at 18 W hotspot) and coolant-side temperature rise to assess margin against an 85 C component limit under nominal and acceptance-test conditions.</t>
+          <t>Conjugate heat transfer model of a 250 W avionics stack on an Al 6061 cold plate with serpentine channels, forced convection from a 24 V brushless fan, and 25 C EGW coolant loop. Model used to determine thermal margin for all components against an 85 C junction temperature limit under nominal and acceptance-test operating conditions.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1345,9 +1305,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1408,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1476,7 +1436,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>All avionics components on the cold-plate assembly must remain below 85 C under nominal operating conditions (245 W, 24 V fan, 25 C coolant inlet) with adequate margin demonstrated by the CHT model.</t>
+          <t>All avionics components on the cold-plate assembly must remain below 85 C junction temperature under all defined operating conditions, with positive margin demonstrated by the CHT model.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1498,12 +1458,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2023R1 CHT Model (GETU-CHT)</t>
+          <t>ANSYS Fluent 2023R1 CHT Model</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer model coupling solid conduction, forced convection (SST k-ω air side, k-ε realizable coolant side), and optional surface-to-surface/DO radiation for the avionics bay cold-plate assembly.</t>
+          <t>Conjugate heat transfer simulation coupling solid conduction, forced convection (SST k-ω air side, k-ε realizable coolant side), and optional surface-to-surface or DO radiation for the avionics bay cold-plate assembly.</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1480,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Thermocouple and IR measurements from TVAC nitrogen-purge chamber test at 24 C, 18 V fan, 25 C coolant, including six component-case thermocouples and two cold-plate inlet/outlet sensors.</t>
+          <t>Thermocouple and IR spot-check measurements from TVAC chamber test with nitrogen purge at 24 C, fan at 18 V, coolant at 25 C / 0.45 kg/min, and 210–215 W measured dissipation; provides validation comparators for CFD predictions.</t>
         </is>
       </c>
     </row>
@@ -1537,24 +1497,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Component-level electrical dissipation map (245 W nominal with 12 W FPGA idle margin in Rev 5; Rev 6 removes margin) used as heat-load boundary conditions; test article dissipated 210–215 W.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Granta MI 2022 Material Properties</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Temperature-dependent thermal conductivity for Al 6061-T6 and other material properties sourced from Granta MI 2022 database; PCB orthotropic properties and TIM conductivity from vendor datasheet.</t>
+          <t>Board-level electrical dissipation map used as heat load boundary conditions; Rev 5 (245 W including 12 W FPGA idle margin) used in baseline CFD; Rev 6 (removes FPGA idle margin, matching test conditions) exists in email but not merged into repo.</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1991,7 +1934,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Component Temperature Comparison — CFD vs. TVAC Test</t>
+          <t>Mesh Convergence / GCI Study</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2006,27 +1949,27 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Medium mesh CHT predictions (radiation off, 20 C air inlet, 245 W, 18 V fan curve scaled linearly) compared against TVAC thermocouple measurements at six component locations and cold-plate inlet/outlet.</t>
+          <t>Three-mesh refinement study (Coarse 3.1 M, Medium 9.2 M, Fine 18.7 M cells) on U3 junction temperature. GCI computed between mesh levels; apparent order p=1.9.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>TVAC hardware test data (TL-GETU-042)</t>
+          <t>Richardson extrapolation / GCI metric</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>If Yes, describe the method</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Grid Convergence Index (GCI)</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>U3 case: −3.7 C (CFD 78.4 C vs. Test 82.1±0.5 C); VRM bank: +1.4 C; Cold-plate ΔT: −0.2 C; Board ambient: +3.5 C; up to 11% error at T3 when normalized to ΔT above inlet</t>
+          <t>GCI Medium-to-Fine 0.8%, Coarse-to-Medium 1.5%; p=1.9</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2038,7 +1981,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence / GCI Study</t>
+          <t>CFD vs Hardware Temperature Comparison</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2048,12 +1991,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Three-mesh study (Coarse 3.1 M, Medium 9.2 M, Fine 18.7 M cells) with GCI computed on U3 junction temperature to assess discretization error; apparent order p=1.9.</t>
+          <t>Comparison of CFD-predicted component case temperatures and coolant-side delta-T against TVAC thermocouple measurements at 6 component locations and 2 cold-plate inlet/outlet sensors.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI framework</t>
+          <t>TVAC test data (TL-GETU-042)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2063,12 +2006,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI)</t>
+          <t>Monte Carlo (200 samples) on TIM k, contact conductance, heat load partition; 95% interval reported</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>GCI Medium→Fine: 0.8%; GCI Coarse→Medium: 1.5%; however refinement not strictly uniform (prism layers and geometry changed between Fine and Medium)</t>
+          <t>U3 case: CFD 78.4 C vs Test 82.1±0.5 C (−3.7 C, ~4.5%); cold-plate ΔT: CFD 2.3 C vs Test 2.5 C (−8%); T3 normalized ΔT error up to 11%; board ambient: CFD 35.2 C vs Test 31.7 C (3.5 C mismatch due to inlet temp error)</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2080,7 +2023,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Fan Curve Verification in Clean Duct</t>
+          <t>Energy Balance Closure Check</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2090,12 +2033,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Fan pressure-jump boundary condition reproduced vendor curve (Delta BFB1012) within ±3% at 12 V and 24 V in an isolated clean-duct model.</t>
+          <t>Global energy imbalance across solid and fluid zones checked at convergence; fan jump curve reproduced against vendor data in clean duct model.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Vendor fan curve data</t>
+          <t>Vendor fan curve (Delta BFB1012) and energy conservation</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2105,7 +2048,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>±3% vs. vendor curve at both operating voltages</t>
+          <t>Energy imbalance &lt;0.2%; fan curve within ±3% at 12 V and 24 V</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2117,7 +2060,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Energy Balance Closure Check</t>
+          <t>TIM Sensitivity / Monte Carlo UQ</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2127,69 +2070,32 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Overall energy imbalance across solids and fluid domains checked on final reported iteration to confirm conservation.</t>
+          <t>Parametric sensitivity of U3 temperature to TIM conductivity (±20%), standoff contact conductance (×0.5), fan voltage scaling (18→24 V), and heat load partition. Monte Carlo (200 samples) on three inputs yielding 95% prediction interval.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Zero-imbalance target</t>
+          <t>Baseline CFD prediction (U3 78.4 C)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Monte Carlo (200 samples); bounded sensitivity cases</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Energy imbalance &lt; 0.2%</t>
+          <t>U3 95% interval: 78.4±2.7 C; TIM ±20%: ±~2 C; standoff ×0.5: +1.1 C</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>TIM Conductivity and Contact Conductance Sensitivity / Monte Carlo UQ</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Monte Carlo UQ (200 samples) varying TIM k (±20%), contact conductance (×0.5), and heat-load partition to quantify uncertainty in U3 junction temperature; separate bounded cases for radiation effect.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Deterministic baseline prediction</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Monte Carlo (200 samples)</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>95% interval U3: 78.4 ± 2.7 C at 245 W / 24 V baseline; radiation sensitivity: −1.6 C at U3; radiation and gas species excluded from Monte Carlo</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Inconclusive</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2244,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented quality processes; version control for all cases; double precision; licensed features verified</t>
+          <t>Commercial solver with documented QA processes; version control of all simulation cases; consistent solver version across study.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>ANSYS Fluent 2023R1 is a commercial solver with implicit quality pedigree; double precision and license feature verification noted. However, one parameter sweep was executed in 2022R2 without documentation, the 18 V fan curve was scaled outside the repository and not pushed to Git before validation, and the Rev C mesh was generated locally and not yet tagged. These configuration-control gaps reduce confidence below the level expected for a medium-assurance study.</t>
+          <t>ANSYS Fluent 2023R1 is a commercial solver with known QA pedigree; double precision and HPC settings documented. However, a sensitivity sweep was executed in 2022R2 without notation, and a manually scaled fan curve was not pushed to the GitLab repository before the validation comparison. These version-control and configuration gaps reduce confidence in software QA for this specific study.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2372,12 +2278,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Solver verified against known benchmarks or analytical solutions for CHT problems</t>
+          <t>Governing equations solved correctly; comparison to analytical solutions or benchmark problems for at least one key sub-model.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>No explicit benchmark or manufactured-solution verification study is cited in the documents. The fan-curve reproduction in the clean duct (±3%) provides partial indirect evidence that the pressure-jump implementation is correct, and the energy-balance closure (&lt;0.2%) is consistent with correct conservation-equation implementation. Reliance on commercial solver reputation fills remaining gaps, supporting a basic level of evidence.</t>
+          <t>Fan pressure-jump sub-model verified against vendor curve within ±3% in a clean duct benchmark. Energy balance verified to &lt;0.2%. No explicit method of manufactured solutions or analytical benchmark for the full CHT domain. ANSYS Fluent's turbulence and heat transfer solvers rely on vendor verification not independently documented here.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2406,12 +2312,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Formal mesh convergence study with GCI &lt; 1% on QoI; uniform refinement ratio; y+ consistent with wall treatment</t>
+          <t>GCI &lt;2% on all quantities of interest; uniform refinement ratio; y+ consistent with turbulence wall treatment across all meshes used in validation.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>A three-mesh GCI study was performed (GCI Medium→Fine 0.8%, Coarse→Medium 1.5%, apparent order p=1.9), which nominally meets a 1% GCI target. However, the refinement is not strictly uniform—the Fine mesh changed prism-layer count and altered the fan shroud fillet geometry (CAD Rev C), undermining GCI applicability. Critically, the validation run used Rev B Medium mesh where a mesher crash omitted three prism layers, resulting in median y+~35 on the air-side cold plate against a target of 1–5 for SST k-ω. This nonconformance was identified but not corrected before the V&amp;V comparison, significantly limiting confidence in discretization adequacy.</t>
+          <t>GCI computed for U3 junction temperature: 0.8% (Medium→Fine), 1.5% (Coarse→Medium), apparent order p=1.9. However, refinement is not strictly uniform (Fine altered prism layers and CAD fillet vs Medium), complicating GCI applicability. Critically, the validation run used Rev B Medium mesh where a mesher crash omitted three prism layers, yielding median y+=35 on the air-side cold plate against an SST target of 1–5. This known nonconformance in the actual validation mesh is unresolved.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2440,12 +2346,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Residual targets met; energy imbalance documented; initialization strategy documented</t>
+          <t>Residuals converge to target levels; energy imbalance documented; solver settings appropriate for physics.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Residual targets of 1e-5 for all equations are stated and reported as achieved. Energy imbalance is &lt;0.2% on the final reported state. A first-order/second-order initialization sequence for the coolant side is documented. These collectively provide adequate evidence of solver convergence.</t>
+          <t>Residual target 1e-5 for all equations; global energy imbalance &lt;0.2% on final reported state, both explicitly documented. Coupled pressure-velocity scheme used; first-order initialization for coolant side to damp recirculation, then second-order — appropriate practice. Convergence monitoring is adequately described.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2474,12 +2380,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent peer review of setup, boundary conditions, mesh quality, and post-processing; all checklist items closed</t>
+          <t>Independent peer review completed; boundary conditions and mesh quality checks signed off; model setup traceable to controlled inputs.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>A two-person review was conducted (J. Hall email approval); geometry and mesh were scripted via journal/Scheme macros improving repeatability. However, the mesh QA checklist has a y+ line item left "TBD" / "pending verification," the design review deck incorrectly claimed peer review complete, the 18 V fan curve modification was made outside the repository, and the Rev C mesh was not version-controlled. Power Map Rev 6 exists only in email and was not merged. These gaps indicate the independent-review process was incomplete.</t>
+          <t>Two-person review performed (J. Hall email approval for numerics and setup). However, the mesh QA checklist y+ line item was left "TBD" / "pending verification of near-wall criteria" despite the design review deck claiming "peer review complete." The manually adjusted 18 V fan curve was not committed to the repository. Power Map Rev 6 (matching test conditions) was not merged. These gaps represent material use errors that were identified but not resolved before the V&amp;V comparison.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2508,12 +2414,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equation choices justified; turbulence model selection supported; known limitations documented and bounded</t>
+          <t>Turbulence model selection justified for flow regime; steady-state assumption justified or transient effects bounded; radiation inclusion/exclusion justified with quantified effect.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Steady RANS SST k-ω for the air side and k-ε realizable for the coolant side are identified with brief justification (vendor pressure-drop curve consistency). Boussinesq buoyancy is noted. However, the steady-state assumption is challenged by observed 8–10 Hz fan PWM tonal and accelerometer evidence; the report acknowledges this but relies on an unvalidated estimate of 200 s thermal time constant. Radiation was disabled in the baseline validation run with a qualitative "forced-convection dominant" justification, but the sensitivity run showed a several-degree effect and revealed emissivity assignment errors (0.85 vs. 0.6 for conformal coating). Nitrogen vs. air gas-property mismatch in the test environment is acknowledged but not corrected. These unresolved model-form issues reduce the achieved level.</t>
+          <t>SST k-ω selected for air side and k-ε realizable for coolant side with rationale tied to pressure-drop correlation consistency. Boussinesq buoyancy included. Steady-state assumption justified by estimated 200 s thermal time constant vs 10 Hz PWM, but the observed 8–10 Hz fan tone in the accelerometer trace was not resolved by transient analysis. Radiation omitted in primary run without quantified justification; sensitivity later showed 1.6–2.1 C effect, which is material relative to 6.6 C margin. Emissivity values later found to be inconsistent with conformal coating properties.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2542,12 +2448,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties from traceable sources; boundary conditions from calibrated measurements; input uncertainties characterized; geometry from controlled CAD</t>
+          <t>Material properties from controlled sources; boundary conditions traceable to measurements; all significant inputs characterized with uncertainty.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Al 6061-T6 k(T) from Granta MI 2022 provides traceable material data. TIM conductivity is reduced from datasheet (3.0 to 2.5 W/m-K) to reflect assembly average without coupon testing. Board-to-standoff contact conductance is borrowed from a 2019 campaign with no retest after new anodize. Emissivity values were later found to be incorrect (0.85 vs. ~0.6 for conformal coating). The power map mismatch (245 W CFD vs. 210–215 W test) was not corrected in the baseline validation case. Fan curve at 18 V was scaled linearly from 24 V data outside the repository. Air properties at constant density (1.184 kg/m³) were used despite test being conducted in nitrogen. Monte Carlo UQ covers only TIM k, contact conductance, and heat-load partition, omitting radiation and gas species. Multiple input gaps limit the achieved level.</t>
+          <t>Al 6061 k(T) from Granta MI (controlled database); PCB orthotropic properties defined. TIM2 conductivity set to 2.5 W/m-K (derated from 3.0 W/m-K datasheet) without new coupon test. Board-to-standoff contact conductance borrowed from 2019 campaign with different anodize; no retest. Inlet temperature initially set to 20 C (incorrect); corrected to 23 C in later revision. Air modeled with constant air properties; N2 used in test (μ +7%) was not modeled. Power map mismatch (245 W CFD vs 210–215 W test) is a significant unresolved input discrepancy.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2576,12 +2482,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative; number of test articles documented; sample adequacy addressed</t>
+          <t>Test article representative of production configuration; number of test runs documented; sample adequacy addressed.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>A single TVAC test article is described. The report references one test run (TL-GETU-042). No information is provided on whether multiple units were tested, production representativeness is confirmed, or sample-size justification is given. The test article power dissipation (210–215 W) differed from the nominal design (245 W), and the test was conducted with nitrogen rather than air. Basic evidence of a single hardware test exists but without statistical characterization or multiple specimens.</t>
+          <t>A single hardware article was tested in the TVAC chamber (TL-GETU-042). The article appears to be a development unit representative of the design. No information on replicate tests or statistical characterization of unit-to-unit variability. Single-article single-run basis is minimally adequate for this MRL.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2610,12 +2516,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled test environment; measurement uncertainty reported; test conducted per documented procedure</t>
+          <t>Calibrated instrumentation with stated uncertainty; test environment (pressure, temperature, flow) controlled and measured; test standard or protocol referenced.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Six thermocouples and IR spot checks are described; coolant inlet/outlet sensors are present. Measurement uncertainty on thermocouples is partially stated (±0.5 C at U3). A test log (TL-GETU-042) is referenced, indicating a documented procedure. However, the overall thermocouple calibration traceability, environmental control details, and full uncertainty budget are not reported. The T12 sensor anomaly ("lift-off likely") is unresolved and flagged but not corrected. Fan tonal behavior (8–10 Hz) was observed in accelerometry but not characterized thermally during the test. Evidence is basic but incomplete.</t>
+          <t>Six thermocouples (T3–T8) on component cases and two on coolant inlet/outlet; IR spot checks for board backside. Thermocouple uncertainty stated as ±0.5 C at U3. Coolant flow (0.45 kg/min) and fan voltage (18 V constant) documented. Chamber temperature 24 C. Observed fan acoustic tone at 8–10 Hz in accelerometer trace is noteworthy. However, T12 deviation flagged as "sensor lift-off likely" without confirmation; FPGA margin not energized per test conductor but not formally documented in test log. No calibration certificates or test standard references cited.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2644,12 +2550,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>CFD model inputs match test conditions; all significant differences identified and their effect quantified</t>
+          <t>CFD boundary conditions match test conditions with documented traceability; all material deviations (fluid species, power level, fan operating point) resolved or bounded.</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Multiple significant mismatches between CFD inputs and test conditions are identified and not reconciled in the validation baseline: (1) Power map 245 W CFD vs. 210–215 W test (FPGA margin not energized); (2) Air properties used in CFD vs. nitrogen in test (μ +7%); (3) Fan curve at 18 V scaled linearly from 24 V data vs. actual fan operation; (4) Air inlet temperature 20 C in initial cases vs. 23–24 C in test; (5) Radiation disabled in baseline despite measured effect of several degrees. None of these are formally corrected in the reported validation comparison, and their combined effect is not quantified. The proposed next steps call for a corrected rerun but it has not been performed.</t>
+          <t>Multiple significant mismatches exist between baseline CFD and test conditions that were not resolved before validation comparison: (1) CFD used 245 W vs test 210–215 W; (2) CFD used air properties vs test N2 purge (μ +7%); (3) CFD fan curve is 24 V scaled linearly to 18 V outside repo vs actual 18 V hardware operation; (4) CFD inlet temperature 20 C vs test 24 C (only corrected in Rev C rerun); (5) radiation excluded in primary comparison. These collectively undermine the equivalency of the validation comparison.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2678,12 +2584,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison at multiple points; consistent normalization; uncertainty bands on both prediction and measurement; statistical validation metrics</t>
+          <t>Quantitative comparison at all instrumented locations; error within defined acceptance bounds; uncertainty bands reported and applied consistently; normalization consistent.</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Point-by-point comparisons are provided at six thermocouple locations and cold-plate ΔT. Absolute differences are reported (U3: −3.7 C, VRM: +1.4 C, cold-plate ΔT: −0.2 C). However, the summary claim of "within 3% on all key points" is contradicted by the detailed table showing up to 11% error at T3 when normalized to ΔT above inlet, indicating inconsistent normalization. The board ambient discrepancy (3.5 C) is partly attributed to an uncorrected inlet temperature. Prediction uncertainty (±2.7 C, 95%) is available from Monte Carlo but is not formally overlaid with measurement uncertainty in the comparison. The T12 anomaly is flagged but unresolved. Overall, quantitative comparison exists but with significant normalization inconsistencies and unresolved outliers.</t>
+          <t>Comparison table provided for U3 (−3.7 C), VRM (+1.4 C), cold-plate ΔT (−0.2 C), and board ambient (3.5 C mismatch tied to inlet error). Monte Carlo 95% interval for U3 reported (±2.7 C). However, the summary slide claim of "within 3% on all key points" is contradicted by up to 11% error at T3 when normalized to ΔT above inlet. Board ambient mismatch traced to an uncorrected model input (20 C vs 23 C inlet). T12 12 K deviation flagged but not resolved. Radiation-on Rev C rerun improves U3 but introduces new T12 discrepancy. Normalization inconsistency not resolved.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2712,12 +2618,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoI (component junction/case temperatures, cold-plate ΔT) directly maps to the 85 C limit and can be measured both computationally and experimentally</t>
+          <t>QoIs directly address component temperature margin against 85 C limit; measurable both computationally and experimentally.</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>The primary QoI—component case temperatures (especially U3 ASIC) and cold-plate coolant ΔT—directly address the 85 C design limit and are measurable both in the simulation and via thermocouples/IR in hardware testing. The model outputs map clearly to the safety/performance requirement. Margin assessment against the 85 C limit is the stated purpose and is evaluated in the report.</t>
+          <t>The primary QoI (component junction/case temperature, particularly U3 and VRM) directly addresses the 85 C limit requirement. Cold-plate ΔT is a secondary QoI relevant to coolant system sizing. All QoIs are measurable by thermocouple in test and are direct outputs of the CHT model. The margin (6.6 C nominal CFD, 2.9 C in test conditions) is quantified against the limit. QoI selection is appropriate and well-aligned with the COU decision.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2746,12 +2652,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (power level, fan voltage, fluid, geometry) match the nominal COU; gaps identified and bounded</t>
+          <t>Validation test conditions span the COU operating envelope including nominal and worst-case operating points; fan speed, power level, coolant conditions, and ambient temperature in test match COU.</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>The validation test captures the same physical configuration (cold plate, PCBs, fan, coolant loop) and relevant QoIs, but departs from the nominal COU in several key respects: test used nitrogen (not air), 18 V fan (not 24 V nominal), 210–215 W (not 245 W), and a single operating point. The 10 Hz fan PWM observed under flight software is not covered by either the steady CFD or the static test. The proposed corrected validation rerun and transient analysis have not been completed. These gaps mean the validation activities are related to but do not fully cover the COU envelope.</t>
+          <t>The validation test approximates the COU geometry and general physics regime but has multiple condition gaps relative to the actual COU: (1) test used N2 purge, not air; (2) test power 210–215 W vs COU nominal 245 W; (3) fan at 18 V constant vs COU nominal 24 V and flight-software 10 Hz PWM; (4) transient fan PWM effect not validated. The coolant conditions (25 C, 0.45 kg/min) do match. Open action items (transient slice, corrected gas properties, aligned power map) would improve relevance but are not yet completed.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2936,7 +2842,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model for the GETU avionics cold plate is not accepted for the stated context of use in its current state. Multiple critical deficiencies prevent acceptance: (1) The validation baseline contains unreconciled input mismatches (power level, working fluid, fan voltage, inlet temperature) that collectively exceed the predicted thermal margin (6.6 C headroom) and have not been corrected or formally bounded; (2) The validation mesh (Rev B Medium) has a documented y+ nonconformance (~35 vs. target 1–5 for SST k-ω) that was identified but not resolved before the V&amp;V comparison, undermining turbulence model fidelity; (3) Configuration control gaps (fan curve edited outside repository, Rev C mesh untagged, two solver versions used without documentation, Power Map Rev 6 not merged) compromise reproducibility; (4) The peer-review checklist was not closed; (5) The steady-state assumption is challenged by observed flight-software fan PWM with no transient analysis completed. Acceptance is contingent on completion of the proposed corrective actions: corrected validation rerun with matched boundary conditions (N2, 18 V, 210–215 W, 23 C inlet, radiation included), rebuilt mesh achieving target y+, transient PWM analysis, closed review checklist, and tagged version control for all cases.</t>
+          <t>The CHT model exhibits several unresolved deficiencies that collectively prevent acceptance for the stated COU at this time. Key issues include: (1) the validation mesh (Rev B Medium) has a documented y+ nonconformance (median ~35 vs SST target 1–5) on the critical air-side cold plate surface that was not corrected before the V&amp;V comparison; (2) significant boundary condition mismatches between CFD and test conditions (35 W power map discrepancy, N2 vs air fluid properties, linear fan curve extrapolation outside version control) undermine the validity of the comparison; (3) the normalization inconsistency in the output comparison table means the stated "within 3%" claim is not supported — errors up to 11% at T3 on a ΔT basis are present; (4) the steady-state assumption in the presence of an observed 8–10 Hz fan tone has not been verified by transient analysis; (5) configuration control gaps (untagged Rev C mesh, unmerged Power Map Rev 6, solver version change in sensitivity sweep) compromise traceability. The model may be accepted following completion of the 2-week sprint action items: corrected mesh with enforced y+, aligned validation rerun (N2, 18 V nonlinear fan curve, 210–215 W Rev 6 power map, radiation on), transient verification of PWM thermal ripple, UQ update including emissivity and nitrogen viscosity, and resolution of all version-control and review-checklist items.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
